--- a/murray-state-scouting/Murray_State_Stats.xlsx
+++ b/murray-state-scouting/Murray_State_Stats.xlsx
@@ -14,6 +14,15 @@
     <sheet name="October Only" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Team Game Log" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'Combined Stats'!$A:$B,'Combined Stats'!$4:$4</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">'October Only'!$A:$B,'October Only'!$4:$4</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">'Player Game Log'!$4:$4</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">'Team Game Log'!$A:$C,'Team Game Log'!$4:$4</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'Combined Stats'!$4:$4,'Combined Stats'!$A:$B</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">'October Only'!$4:$4,'October Only'!$A:$B</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">'Team Game Log'!$4:$4,'Team Game Log'!$A:$C</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -988,7 +997,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -1166,12 +1175,12 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.5"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
-    <oddFooter/>
+    <oddFooter>&amp;L&amp;A&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1179,7 +1188,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:W64"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -5440,12 +5449,12 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.5"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
-    <oddFooter/>
+    <oddFooter>&amp;L&amp;A&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -5453,7 +5462,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:AF23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -7464,12 +7473,12 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.5"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
-    <oddFooter/>
+    <oddFooter>&amp;L&amp;A&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -7477,7 +7486,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:AF21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -9483,12 +9492,12 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.5"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
-    <oddFooter/>
+    <oddFooter>&amp;L&amp;A&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -9496,7 +9505,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:BJ13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -10903,12 +10912,12 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.5"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="3" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
-    <oddFooter/>
+    <oddFooter>&amp;L&amp;A&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/murray-state-scouting/Murray_State_Stats.xlsx
+++ b/murray-state-scouting/Murray_State_Stats.xlsx
@@ -35,7 +35,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="156">
   <si>
-    <t xml:space="preserve">Murray State scouting notes, for the exhibition on Thursday, Oct 22, 2026</t>
+    <t xml:space="preserve">FIU Men's Basketball: Murray State scouting report (exhibition, Thu. Oct. 22, 2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Built from 5 box scores: Team Barcelona (Aug 4), Maroussi BC (Aug 8), France (Aug 10), at Wichita State (Oct 7), vs Incarnate Word (Oct 18).</t>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">Record</t>
   </si>
   <si>
-    <t xml:space="preserve">5–0 (2–0 in October)</t>
+    <t xml:space="preserve">5-0 (2-0 in October)</t>
   </si>
   <si>
     <t xml:space="preserve">Points per game</t>
@@ -62,61 +62,61 @@
     <t xml:space="preserve">Team 3PT%</t>
   </si>
   <si>
-    <t xml:space="preserve">Keys for the staff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ball security is the game.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">They forced 22.8 turnovers per game (28% of opponent possessions) and averaged 15.4 steals. Wichita State kept it to 15 turnovers and was the only team to stay close (93–87).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domon (#77) is the focal point.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2 ppg, 23.5 in October, 30 vs UIW. 26-30 FT but 6-30 from three (20%). Keep him out of the lane, don't foul, make him shoot threes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run Shorter (#34) off the line.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 of his 35 shots are threes (10-29, 34%). 4-7 from three at Wichita State.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attack Rogers (#11).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starter and top rebounder (6.6 rpg), but 25 fouls in 5 games, 0 three-point attempts, 8-14 FT.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pressure Magwood (#0).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backup PG with 20 turnovers in 5 games (4 in each October game).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Box out.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 offensive rebounds per game; 36% of their own misses. 22 second-chance points vs UIW, 25 vs France.</t>
+    <t xml:space="preserve">Keys to the game</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value the ball.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They force 22.8 TO/g (28% of opp. possessions) and get 15.4 steals/g. 31 and 32 pts off TO vs Barcelona and France. Wichita St. had 15 TO and lost by 6.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wall off #77 Domon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2 ppg, 23.5 in Oct., 30 vs UIW. 26-30 FT, 6-30 from 3. Keep him out of the paint and off the line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No space for #34 Shorter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Almost all 3s (10-29). Hard closeouts, make him drive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go at #11 Rogers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 fouls in 5 games. Hasn't shot a 3. 8-14 FT. Sag off him on D.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pressure #0 Magwood.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backup PG. 20 TO in 5 games, 4 in each Oct. game.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finish possessions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 OREB/g, 36% of their misses. 22 second-chance pts vs UIW, 25 vs France. Guards rebound.</t>
   </si>
   <si>
     <t xml:space="preserve">Get downhill.</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2 fouls per game. Wichita State went 26-32 at the line with 36 paint points.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Second-half push, deep bench.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">October second halves: 57 and 53 points. 10–14 players play; bench averaged 42 points.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Likely starting five</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#77 Roman Domon (F), #11 Brigham Rogers (F), #14 Lachlan Crate (F), #8 Talis Soulhac (G), #34 Brayden Shorter (G). Same five in both October games.</t>
+    <t xml:space="preserve">They foul (23.2 PF/g). Wichita St. went 26-32 FT with 36 paint pts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expect a second-half run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct. second halves: 57 and 53 pts. Plays 10-14 guys. Bench avg 42 pts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projected starters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#77 Domon (F), #11 Rogers (F), #14 Crate (F), #8 Soulhac (G), #34 Shorter (G). Started both Oct. games.</t>
   </si>
   <si>
     <t xml:space="preserve">Murray State player box scores, one row per player per game</t>
@@ -1163,7 +1163,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="n">
         <v>9</v>
       </c>

--- a/murray-state-scouting/Murray_State_Stats.xlsx
+++ b/murray-state-scouting/Murray_State_Stats.xlsx
@@ -62,61 +62,61 @@
     <t xml:space="preserve">Team 3PT%</t>
   </si>
   <si>
-    <t xml:space="preserve">Keys to the game</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value the ball.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">They force 22.8 TO/g (28% of opp. possessions) and get 15.4 steals/g. 31 and 32 pts off TO vs Barcelona and France. Wichita St. had 15 TO and lost by 6.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wall off #77 Domon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2 ppg, 23.5 in Oct., 30 vs UIW. 26-30 FT, 6-30 from 3. Keep him out of the paint and off the line.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No space for #34 Shorter.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Almost all 3s (10-29). Hard closeouts, make him drive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Go at #11 Rogers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 fouls in 5 games. Hasn't shot a 3. 8-14 FT. Sag off him on D.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pressure #0 Magwood.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backup PG. 20 TO in 5 games, 4 in each Oct. game.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finish possessions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 OREB/g, 36% of their misses. 22 second-chance pts vs UIW, 25 vs France. Guards rebound.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Get downhill.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">They foul (23.2 PF/g). Wichita St. went 26-32 FT with 36 paint pts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expect a second-half run.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oct. second halves: 57 and 53 pts. Plays 10-14 guys. Bench avg 42 pts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projected starters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#77 Domon (F), #11 Rogers (F), #14 Crate (F), #8 Soulhac (G), #34 Shorter (G). Started both Oct. games.</t>
+    <t xml:space="preserve">Keys for the game</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turnovers drive their wins.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murray State forces 22.8 turnovers per game (28% of opponent possessions) and averages 15.4 steals. They scored 31 and 32 points off turnovers against Barcelona and France. Wichita State committed only 15 and lost by 6, the closest game.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domon (#77) is the go-to scorer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2 ppg overall and 23.5 in October. He scores at the rim and the free-throw line (26-30 FT, 87%) but is 6-30 from three (20%).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shorter (#34) is a spot-up shooter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 of his 35 shot attempts are threes (10-29, 34%). He scored 16 at Wichita State on 4-7 from three.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rogers (#11) is foul-prone and doesn't shoot threes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He leads the team in rebounding (6.6 rpg) but has 25 fouls in 5 games, 0 three-point attempts and 8-14 FT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magwood (#0) is turnover-prone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The backup point guard has 20 turnovers in 5 games, including 4 in each October game.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong on the offensive glass.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 offensive rebounds per game, grabbing 36% of their own misses. 22 second-chance points vs UIW and 25 vs France.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They foul often.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2 fouls per game. Wichita State went 26-32 at the line and scored 36 in the paint.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong second halves and a deep bench.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">October second halves: 57 and 53 points. 10 to 14 players get minutes; the bench averaged 42 points.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likely starting five</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#77 Domon (F), #11 Rogers (F), #14 Crate (F), #8 Soulhac (G), #34 Shorter (G). Same five started both October games.</t>
   </si>
   <si>
     <t xml:space="preserve">Murray State player box scores, one row per player per game</t>
@@ -1108,7 +1108,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="n">
         <v>4</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="n">
         <v>8</v>
       </c>
